--- a/login.xlsx
+++ b/login.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ad\Desktop\AUTO TEST\MuaHangOnline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCE4893-36FF-4774-A6D0-91341195D9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94E56FE-396A-4311-8CFB-6848C78690D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <t>userName</t>
   </si>
@@ -67,6 +68,63 @@
   </si>
   <si>
     <t>inValid</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>zipCode</t>
+  </si>
+  <si>
+    <t>blankAll</t>
+  </si>
+  <si>
+    <t>blankFirstName</t>
+  </si>
+  <si>
+    <t>blankLastName</t>
+  </si>
+  <si>
+    <t>blankZipCode</t>
+  </si>
+  <si>
+    <t>textOnlyInput</t>
+  </si>
+  <si>
+    <t>specialCharInput</t>
+  </si>
+  <si>
+    <t>spaceAroundInput</t>
+  </si>
+  <si>
+    <t>Nguyễn</t>
+  </si>
+  <si>
+    <t>12ABC</t>
+  </si>
+  <si>
+    <t>Anh</t>
+  </si>
+  <si>
+    <t>12ABCa</t>
+  </si>
+  <si>
+    <t>12Abc</t>
+  </si>
+  <si>
+    <t>Anh123</t>
+  </si>
+  <si>
+    <t>Nguyễn124</t>
+  </si>
+  <si>
+    <t>!@#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         Anh123     </t>
   </si>
 </sst>
 </file>
@@ -480,4 +538,114 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87BF768B-98A8-41BC-B331-276916F2E76F}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.296875" customWidth="1"/>
+    <col min="2" max="2" width="24.8984375" customWidth="1"/>
+    <col min="3" max="3" width="23.796875" customWidth="1"/>
+    <col min="4" max="4" width="19.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>